--- a/outputs/evaluation/architecture/validation/CF_M04/run_2/CF_M04_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_2/CF_M04_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,17 +496,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>External service used for generating intelligent response suggestions.</t>
+          <t>External service used for generating response suggestions for reviews.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>55, 68, 69</t>
+          <t>55, 68</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -529,100 +529,148 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The system interaction is performed through a mobile application that acts as a frontend, making requests to a backend server.</t>
+          <t>Data format used for requests and responses in the API.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>55, 66</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AU_17, AU_20</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M04_AU17</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>CF_M04_AU29</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Communication is done through an HTTP-based REST API. Data is exchanged in JSON format, using standard HTTP methods such as GET and POST.</t>
+          <t>Communication between the front-end and the back-end is done through a REST API, using JSON format messages for both requests and responses.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.727</v>
+        <v>0.7808</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dependency Inversion</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The domain defines interfaces that are implemented by the infrastructure.</t>
+          <t>The interaction with the system is performed through a mobile application that acts as a frontend, making requests to a backend.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
+          <t>CF_M04_AU17</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Communication is done through an HTTP-based REST API. Data is exchanged in JSON format, using standard HTTP methods such as GET and POST.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.727</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dependency Inversion</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>The domain defines interfaces that are implemented by the infrastructure.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>CF_M04_AU20</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Users: Application customers who use the new features and provide feedback.</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L5" t="n">
         <v>0.6701</v>
       </c>
     </row>
